--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008460309764744066</v>
       </c>
       <c r="C2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>52204889</v>
+        <v>3970541</v>
       </c>
       <c r="L2" t="n">
-        <v>26763227</v>
+        <v>1609321</v>
       </c>
       <c r="M2" t="n">
-        <v>6155058</v>
+        <v>291264</v>
       </c>
       <c r="N2" t="n">
-        <v>249701</v>
+        <v>4677</v>
       </c>
       <c r="O2" t="n">
-        <v>3650955</v>
+        <v>161986</v>
       </c>
       <c r="P2" t="n">
-        <v>1298269</v>
+        <v>4907</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999972939491272</v>
+        <v>0.9999698996543884</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8205620050430298</v>
+        <v>0.7039111256599426</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6898689270019531</v>
+        <v>0.5165290236473083</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6102270483970642</v>
+        <v>0.3755163550376892</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2194212973117828</v>
+        <v>0.04207562282681465</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6557745933532715</v>
+        <v>0.3888164758682251</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7984763383865356</v>
+        <v>0.5062416195869446</v>
       </c>
       <c r="X2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558068513870239</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117310047149658</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579899072647095</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6614375710487366</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019421935081482</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026924819488894</v>
       </c>
       <c r="C3" t="n">
-        <v>1037</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>52204889</v>
+        <v>3970541</v>
       </c>
       <c r="E3" t="n">
-        <v>7902055</v>
+        <v>946948</v>
       </c>
       <c r="F3" t="n">
-        <v>257996</v>
+        <v>46772</v>
       </c>
       <c r="G3" t="n">
-        <v>20605</v>
+        <v>3620</v>
       </c>
       <c r="H3" t="n">
-        <v>19472</v>
+        <v>4574</v>
       </c>
       <c r="I3" t="n">
-        <v>1157</v>
+        <v>142</v>
       </c>
       <c r="J3" t="n">
-        <v>120833381</v>
+        <v>10069429</v>
       </c>
       <c r="K3" t="n">
-        <v>125168782</v>
+        <v>9773222</v>
       </c>
       <c r="L3" t="n">
-        <v>145313892</v>
+        <v>11556223</v>
       </c>
       <c r="M3" t="n">
-        <v>181804570</v>
+        <v>14985503</v>
       </c>
       <c r="N3" t="n">
-        <v>195028012</v>
+        <v>16219284</v>
       </c>
       <c r="O3" t="n">
-        <v>188948281</v>
+        <v>15648251</v>
       </c>
       <c r="P3" t="n">
-        <v>194341741</v>
+        <v>16217164</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.864216148853302</v>
+        <v>0.7984784245491028</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6750433444976807</v>
+        <v>0.479899674654007</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5468254685401917</v>
+        <v>0.3078493773937225</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2321307957172394</v>
+        <v>0.05183075368404388</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5958523750305176</v>
+        <v>0.3156871199607849</v>
       </c>
       <c r="W3" t="n">
-        <v>0.558973491191864</v>
+        <v>0.02528729662299156</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2382014</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>102565</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>82163</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120835440</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>133910484</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>153853413</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>184139493</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>195552500</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>190264326</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>194510227</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957497239112854</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097340106964111</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569492101669312</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.660748302936554</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9012896418571472</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03198862993387096</v>
       </c>
       <c r="C4" t="n">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>10455808</v>
+        <v>1476800</v>
       </c>
       <c r="E4" t="n">
-        <v>26763227</v>
+        <v>1609321</v>
       </c>
       <c r="F4" t="n">
-        <v>2041609</v>
+        <v>213652</v>
       </c>
       <c r="G4" t="n">
-        <v>121357</v>
+        <v>17203</v>
       </c>
       <c r="H4" t="n">
-        <v>244299</v>
+        <v>35668</v>
       </c>
       <c r="I4" t="n">
-        <v>20194</v>
+        <v>784</v>
       </c>
       <c r="J4" t="n">
-        <v>2059</v>
+        <v>191</v>
       </c>
       <c r="K4" t="n">
-        <v>11416007</v>
+        <v>1670144</v>
       </c>
       <c r="L4" t="n">
-        <v>12031429</v>
+        <v>1506324</v>
       </c>
       <c r="M4" t="n">
-        <v>3931447</v>
+        <v>484372</v>
       </c>
       <c r="N4" t="n">
-        <v>888297</v>
+        <v>106480</v>
       </c>
       <c r="O4" t="n">
-        <v>1916438</v>
+        <v>254627</v>
       </c>
       <c r="P4" t="n">
-        <v>327664</v>
+        <v>4786</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999986469745636</v>
+        <v>0.9999849200248718</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8418234586715698</v>
+        <v>0.7482185363769531</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6823756098747253</v>
+        <v>0.497541069984436</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5767892003059387</v>
+        <v>0.3383326828479767</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2255971878767014</v>
+        <v>0.04644650220870972</v>
       </c>
       <c r="V4" t="n">
-        <v>0.62437903881073</v>
+        <v>0.3484562933444977</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6575965285301208</v>
+        <v>0.04816852882504463</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2497781</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>999552</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>66772</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13821</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2674305</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3491908</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1596524</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>363809</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600393</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566512703895569</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107314348220825</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574692010879517</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6610927581787109</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016157984733582</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>247</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>691977</v>
+        <v>142335</v>
       </c>
       <c r="E5" t="n">
-        <v>3293592</v>
+        <v>404839</v>
       </c>
       <c r="F5" t="n">
-        <v>6155058</v>
+        <v>291264</v>
       </c>
       <c r="G5" t="n">
-        <v>277439</v>
+        <v>26922</v>
       </c>
       <c r="H5" t="n">
-        <v>765789</v>
+        <v>79071</v>
       </c>
       <c r="I5" t="n">
-        <v>71881</v>
+        <v>1663</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8202322</v>
+        <v>1002093</v>
       </c>
       <c r="L5" t="n">
-        <v>12883452</v>
+        <v>1744132</v>
       </c>
       <c r="M5" t="n">
-        <v>5100925</v>
+        <v>654861</v>
       </c>
       <c r="N5" t="n">
-        <v>825990</v>
+        <v>85559</v>
       </c>
       <c r="O5" t="n">
-        <v>2476326</v>
+        <v>351136</v>
       </c>
       <c r="P5" t="n">
-        <v>1024326</v>
+        <v>189143</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999895691871643</v>
+        <v>0.9999883770942688</v>
       </c>
       <c r="R5" t="n">
-        <v>0.900410532951355</v>
+        <v>0.8372175097465515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8735234141349792</v>
+        <v>0.8019946217536926</v>
       </c>
       <c r="T5" t="n">
-        <v>0.954148530960083</v>
+        <v>0.9306022524833679</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9912976622581482</v>
+        <v>0.988301694393158</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9777008295059204</v>
+        <v>0.9630992412567139</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931368231773376</v>
+        <v>0.9881865978240967</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>97322</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1034594</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>119997</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>350660</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2567472</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3578747</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1610177</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>364930</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604826</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733909368515015</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641069173812866</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837216734886169</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963006377220154</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.99388188123703</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983799457550049</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>184992</v>
+        <v>24502</v>
       </c>
       <c r="E6" t="n">
-        <v>243908</v>
+        <v>28002</v>
       </c>
       <c r="F6" t="n">
-        <v>277316</v>
+        <v>24766</v>
       </c>
       <c r="G6" t="n">
-        <v>249701</v>
+        <v>4677</v>
       </c>
       <c r="H6" t="n">
-        <v>109893</v>
+        <v>8140</v>
       </c>
       <c r="I6" t="n">
-        <v>9731</v>
+        <v>143</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78611</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64601</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>131879</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>84061</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>77038</v>
+        <v>23887</v>
       </c>
       <c r="E7" t="n">
-        <v>536451</v>
+        <v>111954</v>
       </c>
       <c r="F7" t="n">
-        <v>1227950</v>
+        <v>167845</v>
       </c>
       <c r="G7" t="n">
-        <v>410045</v>
+        <v>45339</v>
       </c>
       <c r="H7" t="n">
-        <v>3650955</v>
+        <v>161986</v>
       </c>
       <c r="I7" t="n">
-        <v>224701</v>
+        <v>2054</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9726</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358547</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91683</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>299</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>6192</v>
+        <v>2620</v>
       </c>
       <c r="E8" t="n">
-        <v>55423</v>
+        <v>14581</v>
       </c>
       <c r="F8" t="n">
-        <v>126576</v>
+        <v>31337</v>
       </c>
       <c r="G8" t="n">
-        <v>58851</v>
+        <v>13396</v>
       </c>
       <c r="H8" t="n">
-        <v>776985</v>
+        <v>127174</v>
       </c>
       <c r="I8" t="n">
-        <v>1298269</v>
+        <v>4907</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
